--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/ALASKA_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/ALASKA_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RINCÓN DE ROMOS</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C3">
@@ -410,12 +415,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEXICALI</t>
+          <t>Mexicali</t>
         </is>
       </c>
       <c r="C4">
@@ -426,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C5">
@@ -441,12 +451,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DELICIAS</t>
+          <t>Delicias</t>
         </is>
       </c>
       <c r="C6">
@@ -457,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C7">
@@ -472,12 +487,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C8">
@@ -488,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C9">
@@ -501,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C10">
@@ -514,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C11">
@@ -529,12 +559,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TORREÓN</t>
+          <t>Torreón</t>
         </is>
       </c>
       <c r="C12">
@@ -545,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C13">
@@ -560,12 +595,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COLIMA</t>
+          <t>Colima</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COLIMA</t>
+          <t>Colima</t>
         </is>
       </c>
       <c r="C14">
@@ -576,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C15">
@@ -591,12 +631,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAN MIGUEL TOTOLAPAN</t>
+          <t>San Miguel Totolapan</t>
         </is>
       </c>
       <c r="C16">
@@ -607,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TLAPA DE COMONFORT</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C17">
@@ -620,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TLAPEHUALA</t>
+          <t>Tlapehuala</t>
         </is>
       </c>
       <c r="C18">
@@ -633,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C19">
@@ -648,12 +703,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PACHUCA DE SOTO</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C20">
@@ -664,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C21">
@@ -679,12 +739,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C22">
@@ -695,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JALOSTOTITLÁN</t>
+          <t>Jalostotitlán</t>
         </is>
       </c>
       <c r="C23">
@@ -708,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAN MIGUEL EL ALTO</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C24">
@@ -721,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TEPATITLÁN DE MORELOS</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C25">
@@ -734,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZAPOPAN</t>
+          <t>Zapopan</t>
         </is>
       </c>
       <c r="C26">
@@ -747,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C27">
@@ -762,12 +847,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ACUITZIO</t>
+          <t>Acuitzio</t>
         </is>
       </c>
       <c r="C28">
@@ -778,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CARÁCUARO</t>
+          <t>Carácuaro</t>
         </is>
       </c>
       <c r="C29">
@@ -791,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HUETAMO</t>
+          <t>Huetamo</t>
         </is>
       </c>
       <c r="C30">
@@ -804,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INDAPARAPEO</t>
+          <t>Indaparapeo</t>
         </is>
       </c>
       <c r="C31">
@@ -817,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="C32">
@@ -830,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C33">
@@ -845,12 +955,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SANTA MARÍA DEL ORO</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C34">
@@ -861,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C35">
@@ -876,12 +991,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SANTIAGO JUXTLAHUACA</t>
+          <t>Santiago Juxtlahuaca</t>
         </is>
       </c>
       <c r="C36">
@@ -892,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C37">
@@ -907,12 +1027,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HUEHUETLÁN EL GRANDE</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C38">
@@ -923,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C39">
@@ -936,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAN PEDRO CHOLULA</t>
+          <t>San Pedro Cholula</t>
         </is>
       </c>
       <c r="C40">
@@ -949,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C41">
@@ -964,12 +1099,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TOLIMÁN</t>
+          <t>Tolimán</t>
         </is>
       </c>
       <c r="C42">
@@ -980,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C43">
@@ -995,12 +1135,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CULIACÁN</t>
+          <t>Culiacán</t>
         </is>
       </c>
       <c r="C44">
@@ -1011,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ELOTA</t>
+          <t>Elota</t>
         </is>
       </c>
       <c r="C45">
@@ -1024,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C46">
@@ -1039,12 +1189,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TAMPICO</t>
+          <t>Tampico</t>
         </is>
       </c>
       <c r="C47">
@@ -1055,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48">
@@ -1070,12 +1225,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COSCOMATEPEC</t>
+          <t>Coscomatepec</t>
         </is>
       </c>
       <c r="C49">
@@ -1086,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IGNACIO DE LA LLAVE</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C50">
@@ -1099,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAYULA DE ALEMÁN</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C51">
@@ -1112,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TLALIXCOYAN</t>
+          <t>Tlalixcoyan</t>
         </is>
       </c>
       <c r="C52">
@@ -1125,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C53">
@@ -1140,12 +1315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C54">
@@ -1156,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GUADALUPE</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="C55">
@@ -1169,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OJOCALIENTE</t>
+          <t>Ojocaliente</t>
         </is>
       </c>
       <c r="C56">
@@ -1182,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="C57">
@@ -1195,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C58">
@@ -1210,7 +1405,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C59">
@@ -1218,41 +1413,6 @@
       </c>
       <c r="D59">
         <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
